--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
   <si>
     <t>Filename</t>
   </si>
@@ -811,694 +811,667 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9826,0.0043,0.0029,0.0011</t>
+    <t>0.9792,0.0052,0.0030,0.0017</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9895,0.0002,0.0003,0.0061</t>
-  </si>
-  <si>
-    <t>0.0132,0.0000,0.0003,0.9955</t>
+    <t>0.9376,0.0002,0.0001,0.0771</t>
+  </si>
+  <si>
+    <t>0.0092,0.0000,0.0000,0.9980</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9604,0.0029,0.0151,0.0006</t>
+  </si>
+  <si>
+    <t>0.2457,0.0021,0.8082,0.0002</t>
+  </si>
+  <si>
+    <t>0.7342,0.0007,0.4292,0.0001</t>
+  </si>
+  <si>
+    <t>0.0959,0.0002,0.9445,0.0001</t>
+  </si>
+  <si>
+    <t>0.9486,0.0004,0.0399,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.9935,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9775,0.0001,0.0106,0.0008</t>
+  </si>
+  <si>
+    <t>0.1029,0.0013,0.8745,0.0016</t>
+  </si>
+  <si>
+    <t>0.0022,0.0001,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0066,0.0015,0.9902,0.0002</t>
+  </si>
+  <si>
+    <t>0.0373,0.0001,0.9798,0.0001</t>
+  </si>
+  <si>
+    <t>0.0797,0.0004,0.9103,0.0028</t>
+  </si>
+  <si>
+    <t>0.0054,0.0000,0.9960,0.0003</t>
+  </si>
+  <si>
+    <t>0.1880,0.8544,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9547,0.0193,0.0160,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9985,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.9988,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0020,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0150,0.9834,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9984,0.0262,0.0000</t>
+  </si>
+  <si>
+    <t>0.0076,0.9696,0.0187,0.0026</t>
+  </si>
+  <si>
+    <t>0.0068,0.0063,0.9772,0.0027</t>
+  </si>
+  <si>
+    <t>0.0034,0.0047,0.9879,0.0005</t>
+  </si>
+  <si>
+    <t>0.0261,0.0002,0.8637,0.0048</t>
+  </si>
+  <si>
+    <t>0.0061,0.0153,0.9918,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0008,0.9897,0.0063</t>
+  </si>
+  <si>
+    <t>0.0539,0.3834,0.0001,0.2915</t>
+  </si>
+  <si>
+    <t>0.0020,0.9886,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0116,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.9951,0.0019</t>
+  </si>
+  <si>
+    <t>0.0070,0.0001,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9997,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9902,0.8769,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0041,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9973,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.1314,0.0006,0.9053,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0021,0.9989,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9448,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.5352,0.9920,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9650,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9902,0.9865,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0006,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0017,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0028,0.9995</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9786,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9838,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9778,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9973,0.3739,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0112,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0017,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0021,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9430,0.1033,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0005,0.9959,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.0004,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.9702,0.0010,0.0131,0.0008</t>
+  </si>
+  <si>
+    <t>0.0090,0.0002,0.9917,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9974,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0547,0.9574,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9372,0.0051,0.0347,0.0010</t>
+  </si>
+  <si>
+    <t>0.5487,0.0004,0.4849,0.0006</t>
+  </si>
+  <si>
+    <t>0.9630,0.0042,0.0045,0.0018</t>
+  </si>
+  <si>
+    <t>0.7619,0.0036,0.1246,0.0130</t>
+  </si>
+  <si>
+    <t>0.0001,0.5671,0.0003,0.9938</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9078,0.0000</t>
+  </si>
+  <si>
+    <t>0.4567,0.6395,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.6500,0.3697,0.0080,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.7888,0.9918,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9799,0.9907,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0078,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0013,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9381,0.0004,0.0432,0.0013</t>
+  </si>
+  <si>
+    <t>0.1592,0.0000,0.9030,0.0001</t>
+  </si>
+  <si>
+    <t>0.4857,0.0030,0.4873,0.0031</t>
+  </si>
+  <si>
+    <t>0.0038,0.0000,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9958,0.2890,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.3110,0.7999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6145,0.0001,0.0000,0.5888</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0022,0.9994,0.0006</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.2877,0.1057,0.3649,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9831,0.0057,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.0774,0.8609,0.0138,0.0036</t>
+  </si>
+  <si>
+    <t>0.9681,0.0034,0.0148,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0018,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0012,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9538,0.0441,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.4694,0.6729,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.8371,0.2386,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0452,0.0062,0.9693,0.0004</t>
+  </si>
+  <si>
+    <t>0.9869,0.0140,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0014,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9757,0.0103,0.0098,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9854,0.0133,0.0027,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0090,0.0088,0.9542,0.0201</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.1356,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1445,0.0070,0.8229,0.0018</t>
+  </si>
+  <si>
+    <t>0.0070,0.0007,0.9919,0.0002</t>
+  </si>
+  <si>
+    <t>0.0112,0.0050,0.9726,0.0015</t>
+  </si>
+  <si>
+    <t>0.2076,0.0105,0.7730,0.0007</t>
+  </si>
+  <si>
+    <t>0.0189,0.0247,0.9419,0.0006</t>
+  </si>
+  <si>
+    <t>0.8111,0.0018,0.2577,0.0004</t>
+  </si>
+  <si>
+    <t>0.9100,0.0011,0.0174,0.0205</t>
+  </si>
+  <si>
+    <t>0.5744,0.0015,0.4382,0.0010</t>
+  </si>
+  <si>
+    <t>0.1703,0.8855,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9988,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9389,0.0969,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0758,0.9453,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0266,0.9751,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9810,0.0033,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.8498,0.0003,0.1697,0.0006</t>
+  </si>
+  <si>
+    <t>0.9883,0.0003,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.9720,0.0013,0.0058,0.0023</t>
+  </si>
+  <si>
+    <t>0.2955,0.0004,0.7460,0.0009</t>
+  </si>
+  <si>
+    <t>0.0037,0.0016,0.9953,0.0002</t>
+  </si>
+  <si>
+    <t>0.0044,0.0002,0.9909,0.0013</t>
+  </si>
+  <si>
+    <t>0.0314,0.0123,0.9341,0.0012</t>
+  </si>
+  <si>
+    <t>0.0539,0.0005,0.9572,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.0220,0.9789,0.0013</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9639,0.0277,0.0049,0.0035</t>
+  </si>
+  <si>
+    <t>0.9959,0.0029,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0021,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0146,0.0905,0.8934,0.0019</t>
+  </si>
+  <si>
+    <t>0.9793,0.0003,0.0049,0.0054</t>
+  </si>
+  <si>
+    <t>0.3683,0.0005,0.7926,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0049,0.2667,0.8653,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0160,0.0025,0.9768,0.0009</t>
+  </si>
+  <si>
+    <t>0.0095,0.0014,0.9807,0.0025</t>
+  </si>
+  <si>
+    <t>0.0021,0.0031,0.9918,0.0018</t>
+  </si>
+  <si>
+    <t>0.9669,0.0018,0.0119,0.0011</t>
+  </si>
+  <si>
+    <t>0.9953,0.0001,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9902,0.0112,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9381,0.0053,0.0262,0.0011</t>
-  </si>
-  <si>
-    <t>0.0024,0.0004,0.9956,0.0004</t>
-  </si>
-  <si>
-    <t>0.1073,0.0017,0.9301,0.0001</t>
-  </si>
-  <si>
-    <t>0.0096,0.0001,0.9902,0.0004</t>
-  </si>
-  <si>
-    <t>0.9297,0.0010,0.0492,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.9913,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8117,0.0005,0.1475,0.0026</t>
-  </si>
-  <si>
-    <t>0.6202,0.0010,0.4193,0.0007</t>
-  </si>
-  <si>
-    <t>0.0182,0.0001,0.9879,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.0008,0.9927,0.0004</t>
-  </si>
-  <si>
-    <t>0.4966,0.0000,0.7203,0.0001</t>
-  </si>
-  <si>
-    <t>0.0174,0.0008,0.9749,0.0012</t>
-  </si>
-  <si>
-    <t>0.0029,0.0000,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.3004,0.7478,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.4535,0.4645,0.0680,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0024,0.9993,0.0022</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0034,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9891,0.0007,0.0050,0.0005</t>
-  </si>
-  <si>
-    <t>0.1365,0.8987,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9956,0.0395,0.0000</t>
-  </si>
-  <si>
-    <t>0.0461,0.6861,0.0918,0.0041</t>
-  </si>
-  <si>
-    <t>0.1185,0.0057,0.8103,0.0051</t>
-  </si>
-  <si>
-    <t>0.0118,0.0111,0.9687,0.0018</t>
-  </si>
-  <si>
-    <t>0.0062,0.0001,0.9789,0.0016</t>
-  </si>
-  <si>
-    <t>0.0014,0.0043,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9979,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9929,0.0080</t>
-  </si>
-  <si>
-    <t>0.0576,0.1226,0.0009,0.8750</t>
-  </si>
-  <si>
-    <t>0.0012,0.9879,0.0000,0.0029</t>
-  </si>
-  <si>
-    <t>0.0008,0.9976,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0009</t>
+    <t>0.9831,0.0212,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0029,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.0306,0.9604,0.0012</t>
   </si>
   <si>
     <t>0.0003,0.0021,0.9991,0.0001</t>
   </si>
   <si>
-    <t>0.0009,0.0005,0.9967,0.0007</t>
-  </si>
-  <si>
-    <t>0.0420,0.0001,0.9809,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9983,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9995,0.0006</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0016,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0010,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9701,0.0342,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9692,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.0044,0.9877,0.0039</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9991,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9944,0.0000,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.5154,0.0011,0.5433,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0013,0.9993,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9876,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9816,0.9422,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.3940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9892,0.3329,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0024,0.9998</t>
-  </si>
-  <si>
-    <t>0.0013,0.0004,0.0004,0.9990</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9721,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9891,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9873,0.4638,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9898,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9931,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.7299,0.5384,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0030,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0026,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0447,0.0003,0.9837,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0003,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.9896,0.0001,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.0250,0.0003,0.9765,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9983,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9987,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1934,0.8545,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9608,0.0020,0.0199,0.0012</t>
-  </si>
-  <si>
-    <t>0.3395,0.0001,0.6806,0.0005</t>
-  </si>
-  <si>
-    <t>0.8269,0.0043,0.0866,0.0065</t>
-  </si>
-  <si>
-    <t>0.9038,0.0185,0.0248,0.0049</t>
-  </si>
-  <si>
-    <t>0.0002,0.6834,0.0002,0.9764</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9968,0.9619,0.0000</t>
-  </si>
-  <si>
-    <t>0.0896,0.9277,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9761,0.0223,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9975,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0005,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9641,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8013,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0013,0.9916,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4007,0.0054,0.4827,0.0068</t>
-  </si>
-  <si>
-    <t>0.4301,0.0002,0.6702,0.0002</t>
-  </si>
-  <si>
-    <t>0.9874,0.0002,0.0033,0.0007</t>
-  </si>
-  <si>
-    <t>0.0230,0.0000,0.0000,0.9957</t>
-  </si>
-  <si>
-    <t>0.0001,0.9863,0.8820,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9975,0.0008,0.0024</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0133,0.9890,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6907,0.0002,0.0008,0.3300</t>
-  </si>
-  <si>
-    <t>0.0014,0.0023,0.9977,0.0009</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0465,0.9058,0.0230,0.0002</t>
-  </si>
-  <si>
-    <t>0.9893,0.0029,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.1781,0.7664,0.0086,0.0033</t>
-  </si>
-  <si>
-    <t>0.5189,0.0137,0.4244,0.0003</t>
-  </si>
-  <si>
-    <t>0.9946,0.0014,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0011,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9531,0.0300,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.4321,0.6898,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9881,0.0107,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6105,0.0214,0.2803,0.0008</t>
-  </si>
-  <si>
-    <t>0.9800,0.0319,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0017,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0022,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9856,0.0032,0.0059,0.0010</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9881,0.0025,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0043,0.9957,0.0045</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0120,0.9968,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0674,0.0032,0.9109,0.0023</t>
-  </si>
-  <si>
-    <t>0.0459,0.0004,0.9620,0.0008</t>
-  </si>
-  <si>
-    <t>0.0527,0.0187,0.9161,0.0016</t>
-  </si>
-  <si>
-    <t>0.0060,0.0008,0.9926,0.0001</t>
-  </si>
-  <si>
-    <t>0.0556,0.0210,0.8961,0.0005</t>
-  </si>
-  <si>
-    <t>0.4368,0.0034,0.6411,0.0003</t>
-  </si>
-  <si>
-    <t>0.8869,0.0012,0.0552,0.0072</t>
-  </si>
-  <si>
-    <t>0.0055,0.0025,0.9887,0.0002</t>
-  </si>
-  <si>
-    <t>0.0058,0.9917,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3415,0.7462,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.1047,0.9336,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0061,0.9940,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9885,0.0016,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9466,0.0007,0.0426,0.0011</t>
-  </si>
-  <si>
-    <t>0.9473,0.0006,0.0084,0.0089</t>
-  </si>
-  <si>
-    <t>0.8823,0.0171,0.0434,0.0023</t>
-  </si>
-  <si>
-    <t>0.7226,0.0005,0.3236,0.0006</t>
-  </si>
-  <si>
-    <t>0.0065,0.0019,0.9924,0.0005</t>
-  </si>
-  <si>
-    <t>0.0073,0.0010,0.9838,0.0010</t>
-  </si>
-  <si>
-    <t>0.0792,0.0119,0.8895,0.0029</t>
-  </si>
-  <si>
-    <t>0.0029,0.0022,0.9926,0.0004</t>
-  </si>
-  <si>
-    <t>0.0021,0.0221,0.9778,0.0005</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9724,0.0200,0.0015,0.0018</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0025,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0022,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0024,0.9987,0.0006</t>
-  </si>
-  <si>
-    <t>0.1959,0.0805,0.4776,0.0014</t>
-  </si>
-  <si>
-    <t>0.9875,0.0001,0.0022,0.0042</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0026,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0206,0.9908,0.0006</t>
-  </si>
-  <si>
-    <t>0.0019,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9400,0.0002,0.0596,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0019,0.9976,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.0107,0.9976,0.0003</t>
-  </si>
-  <si>
-    <t>0.9640,0.0022,0.0135,0.0009</t>
-  </si>
-  <si>
-    <t>0.9661,0.0002,0.0175,0.0013</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0021,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0046,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0017,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0180,0.0162,0.9304,0.0017</t>
-  </si>
-  <si>
-    <t>0.0011,0.0016,0.9971,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0067,0.9995,0.0004</t>
-  </si>
-  <si>
-    <t>0.0948,0.0563,0.6693,0.0071</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.2959,0.0001,0.4569,0.0090</t>
-  </si>
-  <si>
-    <t>0.0199,0.0106,0.9500,0.0047</t>
-  </si>
-  <si>
-    <t>0.0327,0.0013,0.9570,0.0021</t>
-  </si>
-  <si>
-    <t>0.9951,0.0000,0.0003,0.0028</t>
-  </si>
-  <si>
-    <t>0.0007,0.0016,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0324,0.0000,0.0000,0.9961</t>
-  </si>
-  <si>
-    <t>0.9857,0.0002,0.0000,0.0041</t>
+    <t>0.0024,0.0236,0.9893,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.0095,0.9918,0.0004</t>
+  </si>
+  <si>
+    <t>0.0051,0.0000,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0225,0.0000,0.4390,0.1369</t>
+  </si>
+  <si>
+    <t>0.2434,0.0026,0.6595,0.0048</t>
+  </si>
+  <si>
+    <t>0.0046,0.0008,0.9834,0.0216</t>
+  </si>
+  <si>
+    <t>0.9247,0.0000,0.0018,0.0567</t>
+  </si>
+  <si>
+    <t>0.0039,0.0004,0.0000,0.9987</t>
+  </si>
+  <si>
+    <t>0.0177,0.0000,0.0000,0.9984</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0000,0.0005</t>
   </si>
 </sst>
 </file>
@@ -1982,7 +1955,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1996,7 +1969,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2010,7 +1983,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2024,7 +1997,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2038,7 +2011,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2052,7 +2025,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2039,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2077,10 +2050,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2067,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2108,7 +2081,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2095,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2109,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2123,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2137,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2151,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2192,7 +2165,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2203,10 +2176,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2193,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2207,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2221,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2235,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2249,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2290,7 +2263,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2304,7 +2277,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2291,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,7 +2305,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2319,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,7 +2333,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,7 +2347,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,7 +2361,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2402,7 +2375,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2389,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2403,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2444,7 +2417,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2458,7 +2431,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2445,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2459,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2497,10 +2470,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2487,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2501,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2515,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2529,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2543,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2557,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2571,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2585,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2599,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2613,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2627,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2641,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2655,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2696,7 +2669,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2710,7 +2683,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2724,7 +2697,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2738,7 +2711,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2752,7 +2725,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2766,7 +2739,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2780,7 +2753,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2794,7 +2767,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2808,7 +2781,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2822,7 +2795,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>285</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2836,7 +2809,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2850,7 +2823,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2864,7 +2837,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2878,7 +2851,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2892,7 +2865,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,10 +2876,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2917,10 +2890,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2934,7 +2907,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2948,7 +2921,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2962,7 +2935,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2976,7 +2949,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2990,7 +2963,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3004,7 +2977,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,7 +2991,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3032,7 +3005,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3043,10 +3016,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,7 +3033,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3071,10 +3044,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3085,10 +3058,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3102,7 +3075,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3116,7 +3089,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3130,7 +3103,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3144,7 +3117,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3158,7 +3131,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3172,7 +3145,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3186,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3200,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3214,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3228,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3256,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3270,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>350</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3284,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3298,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3312,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>324</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3299,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3313,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3327,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,7 +3341,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3355,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3369,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3410,7 +3383,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3424,7 +3397,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3438,7 +3411,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>366</v>
+        <v>283</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3452,7 +3425,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,7 +3439,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,7 +3453,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3491,10 +3464,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3508,7 +3481,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3522,7 +3495,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3536,7 +3509,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3550,7 +3523,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>374</v>
+        <v>308</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3564,7 +3537,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>367</v>
+        <v>309</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3551,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,7 +3565,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,7 +3593,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3634,7 +3607,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3621,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>269</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3635,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3649,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3663,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3718,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3732,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3746,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3760,7 +3733,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,7 +3747,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3788,7 +3761,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3802,7 +3775,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3816,7 +3789,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,7 +3803,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3844,7 +3817,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3858,7 +3831,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3872,7 +3845,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3914,7 +3887,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>266</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3925,10 +3898,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3942,7 +3915,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3956,7 +3929,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3970,7 +3943,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3984,7 +3957,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3998,7 +3971,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4009,10 +3982,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +3999,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>324</v>
+        <v>394</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4013,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4027,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4041,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4079,10 +4052,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4124,7 +4097,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4138,7 +4111,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4139,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4180,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4194,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4208,7 +4181,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4222,7 +4195,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4236,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4250,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4264,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,7 +4251,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,7 +4265,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4317,10 +4290,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4334,7 +4307,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4348,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4362,7 +4335,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,7 +4349,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4390,7 +4363,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4404,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4418,7 +4391,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4432,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4446,7 +4419,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4460,7 +4433,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4474,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4488,7 +4461,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4502,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4516,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4530,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4544,7 +4517,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4558,7 +4531,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4572,7 +4545,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4583,10 +4556,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,7 +4573,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,10 +4584,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4628,7 +4601,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4642,7 +4615,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4653,10 +4626,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4670,7 +4643,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,7 +4657,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,7 +4671,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4712,7 +4685,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4726,7 +4699,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4740,7 +4713,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4751,10 +4724,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4768,7 +4741,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,7 +4755,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4796,7 +4769,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4810,7 +4783,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4824,7 +4797,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4838,7 +4811,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4825,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4839,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4853,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>373</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4867,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4881,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>350</v>
+        <v>271</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4950,7 +4923,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4961,10 +4934,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4978,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4992,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5006,7 +4979,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5020,7 +4993,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5034,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5045,10 +5018,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5062,7 +5035,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>471</v>
+        <v>419</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5076,7 +5049,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5090,7 +5063,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5104,7 +5077,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5118,7 +5091,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,7 +5105,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5146,7 +5119,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5160,7 +5133,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5174,7 +5147,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>274</v>
+        <v>469</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5188,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5202,7 +5175,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>324</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5216,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5230,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5244,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5258,7 +5231,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5272,7 +5245,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5286,7 +5259,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5300,7 +5273,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5314,7 +5287,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5328,7 +5301,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5342,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5356,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5370,7 +5343,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5384,7 +5357,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5398,7 +5371,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5440,7 +5413,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,670 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9792,0.0052,0.0030,0.0017</t>
+    <t>0.9621,0.0108,0.0052,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.0029,0.0000,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5735,0.0134,0.1952,0.0057</t>
+  </si>
+  <si>
+    <t>0.0228,0.0015,0.9735,0.0003</t>
+  </si>
+  <si>
+    <t>0.4077,0.0016,0.7022,0.0002</t>
+  </si>
+  <si>
+    <t>0.1054,0.0010,0.9288,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0003,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0068,0.9928,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9586,0.0004,0.0201,0.0019</t>
+  </si>
+  <si>
+    <t>0.5044,0.0001,0.5840,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9993,0.0013</t>
+  </si>
+  <si>
+    <t>0.0035,0.0003,0.9940,0.0003</t>
+  </si>
+  <si>
+    <t>0.0044,0.0001,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.9941,0.0013</t>
+  </si>
+  <si>
+    <t>0.0055,0.0000,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.5053,0.5125,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9852,0.0084,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0095,0.9800,0.0064,0.0001</t>
+  </si>
+  <si>
+    <t>0.9670,0.0146,0.0013,0.0030</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.9932,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9822,0.6692,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.9867,0.0291,0.0008</t>
+  </si>
+  <si>
+    <t>0.1065,0.0023,0.8450,0.0038</t>
+  </si>
+  <si>
+    <t>0.0094,0.0066,0.9790,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.0031,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9981,0.0078</t>
+  </si>
+  <si>
+    <t>0.0039,0.7631,0.0023,0.9254</t>
+  </si>
+  <si>
+    <t>0.0030,0.9867,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.9975,0.0068,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.0090,0.0028,0.9875,0.0006</t>
+  </si>
+  <si>
+    <t>0.0085,0.0013,0.9820,0.0030</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0005,0.9962,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0184,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8640,0.2171,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9807,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9972,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9206,0.0001,0.1442,0.0000</t>
+  </si>
+  <si>
+    <t>0.1202,0.0003,0.9174,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0026,0.9993,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9923,0.8853,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9971,0.8232,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.4595,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.7792,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.0001,0.0004,0.9978</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.0011,0.9992</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0003,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9680,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9829,0.8317,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9391,0.9632,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0027,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9892,0.0096,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0028,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0001,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0079,0.0003,0.9939,0.0001</t>
+  </si>
+  <si>
+    <t>0.9899,0.0002,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9505,0.0001,0.0438,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0809,0.9362,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9742,0.0007,0.0131,0.0008</t>
+  </si>
+  <si>
+    <t>0.9178,0.0004,0.0857,0.0003</t>
+  </si>
+  <si>
+    <t>0.7755,0.0021,0.2036,0.0027</t>
+  </si>
+  <si>
+    <t>0.9391,0.0043,0.0310,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.5920,0.0003,0.9940</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0082,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9864,0.9405,0.0001</t>
+  </si>
+  <si>
+    <t>0.5015,0.6022,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9725,0.0197,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.9786,0.0188,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0118,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9618,0.9870,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0141,0.9933,0.0003</t>
+  </si>
+  <si>
+    <t>0.0107,0.0052,0.9759,0.0011</t>
+  </si>
+  <si>
+    <t>0.8842,0.0002,0.0759,0.0026</t>
+  </si>
+  <si>
+    <t>0.0812,0.0001,0.9457,0.0002</t>
+  </si>
+  <si>
+    <t>0.8934,0.0079,0.0530,0.0048</t>
+  </si>
+  <si>
+    <t>0.0382,0.0000,0.0000,0.9949</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9376,0.0002,0.0001,0.0771</t>
-  </si>
-  <si>
-    <t>0.0092,0.0000,0.0000,0.9980</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9604,0.0029,0.0151,0.0006</t>
-  </si>
-  <si>
-    <t>0.2457,0.0021,0.8082,0.0002</t>
-  </si>
-  <si>
-    <t>0.7342,0.0007,0.4292,0.0001</t>
-  </si>
-  <si>
-    <t>0.0959,0.0002,0.9445,0.0001</t>
-  </si>
-  <si>
-    <t>0.9486,0.0004,0.0399,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.9935,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9775,0.0001,0.0106,0.0008</t>
-  </si>
-  <si>
-    <t>0.1029,0.0013,0.8745,0.0016</t>
-  </si>
-  <si>
-    <t>0.0022,0.0001,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0066,0.0015,0.9902,0.0002</t>
-  </si>
-  <si>
-    <t>0.0373,0.0001,0.9798,0.0001</t>
-  </si>
-  <si>
-    <t>0.0797,0.0004,0.9103,0.0028</t>
-  </si>
-  <si>
-    <t>0.0054,0.0000,0.9960,0.0003</t>
-  </si>
-  <si>
-    <t>0.1880,0.8544,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9547,0.0193,0.0160,0.0006</t>
-  </si>
-  <si>
-    <t>0.0021,0.0003,0.9985,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.9988,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0020,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.0150,0.9834,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0262,0.0000</t>
-  </si>
-  <si>
-    <t>0.0076,0.9696,0.0187,0.0026</t>
-  </si>
-  <si>
-    <t>0.0068,0.0063,0.9772,0.0027</t>
-  </si>
-  <si>
-    <t>0.0034,0.0047,0.9879,0.0005</t>
-  </si>
-  <si>
-    <t>0.0261,0.0002,0.8637,0.0048</t>
-  </si>
-  <si>
-    <t>0.0061,0.0153,0.9918,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0008,0.9897,0.0063</t>
-  </si>
-  <si>
-    <t>0.0539,0.3834,0.0001,0.2915</t>
-  </si>
-  <si>
-    <t>0.0020,0.9886,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0116,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9951,0.0019</t>
-  </si>
-  <si>
-    <t>0.0070,0.0001,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0012,0.9997,0.0004</t>
+    <t>0.0000,0.0001,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9728,0.4765,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.9955,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.3209,0.8091,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8798,0.0001,0.0002,0.1342</t>
+  </si>
+  <si>
+    <t>0.0017,0.0009,0.9976,0.0009</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0791,0.8767,0.0185,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9884,0.0016,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.8497,0.1182,0.0062,0.0012</t>
+  </si>
+  <si>
+    <t>0.8243,0.0074,0.1364,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0011,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9646,0.0300,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9021,0.1431,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9802,0.0185,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9660,0.0012,0.0290,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0046,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0025,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9963,0.0031,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9801,0.0036,0.0087,0.0016</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9829,0.0137,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.0104,0.9797,0.0065</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.1246,0.9955,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0074,0.9970,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.2298,0.0033,0.7053,0.0046</t>
+  </si>
+  <si>
+    <t>0.0038,0.0005,0.9940,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0032,0.9952,0.0002</t>
+  </si>
+  <si>
+    <t>0.6824,0.0284,0.2180,0.0007</t>
+  </si>
+  <si>
+    <t>0.1649,0.0498,0.6037,0.0003</t>
+  </si>
+  <si>
+    <t>0.9412,0.0004,0.0977,0.0001</t>
+  </si>
+  <si>
+    <t>0.9712,0.0018,0.0053,0.0025</t>
+  </si>
+  <si>
+    <t>0.0381,0.0181,0.9097,0.0010</t>
+  </si>
+  <si>
+    <t>0.0192,0.9792,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0255,0.9820,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8723,0.1786,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0194,0.9827,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0640,0.9498,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9538,0.0155,0.0035,0.0003</t>
+  </si>
+  <si>
+    <t>0.9655,0.0009,0.0194,0.0009</t>
+  </si>
+  <si>
+    <t>0.8527,0.0054,0.0032,0.0293</t>
+  </si>
+  <si>
+    <t>0.9219,0.0120,0.0235,0.0024</t>
+  </si>
+  <si>
+    <t>0.8155,0.0016,0.2059,0.0010</t>
+  </si>
+  <si>
+    <t>0.0038,0.0007,0.9953,0.0010</t>
+  </si>
+  <si>
+    <t>0.0023,0.0014,0.9909,0.0016</t>
+  </si>
+  <si>
+    <t>0.0216,0.0189,0.9338,0.0026</t>
+  </si>
+  <si>
+    <t>0.0081,0.0042,0.9822,0.0003</t>
+  </si>
+  <si>
+    <t>0.0065,0.0131,0.9619,0.0017</t>
+  </si>
+  <si>
+    <t>0.9975,0.0015,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9882,0.0072,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9930,0.0057,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9861,0.0154,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0014,0.9959,0.0014</t>
+  </si>
+  <si>
+    <t>0.0559,0.0690,0.7422,0.0014</t>
+  </si>
+  <si>
+    <t>0.9782,0.0006,0.0084,0.0020</t>
+  </si>
+  <si>
+    <t>0.0037,0.0007,0.9976,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0055,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.2733,0.9591,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0002,0.9948,0.0005</t>
+  </si>
+  <si>
+    <t>0.0379,0.0002,0.9545,0.0013</t>
+  </si>
+  <si>
+    <t>0.0005,0.0020,0.9976,0.0003</t>
+  </si>
+  <si>
+    <t>0.9033,0.0105,0.0366,0.0021</t>
+  </si>
+  <si>
+    <t>0.9905,0.0001,0.0030,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0005,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9946,0.0042,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9987,0.0010,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9986,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9902,0.8769,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0041,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9973,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.1314,0.0006,0.9053,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0021,0.9989,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9448,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.5352,0.9920,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.9650,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9902,0.9865,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0006,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0017,0.9998</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0028,0.9995</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.9786,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9838,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9925,0.9778,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9972,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.3739,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.0112,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0017,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9430,0.1033,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.0005,0.9959,0.0004</t>
-  </si>
-  <si>
-    <t>0.0024,0.0004,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.9702,0.0010,0.0131,0.0008</t>
-  </si>
-  <si>
-    <t>0.0090,0.0002,0.9917,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9974,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0547,0.9574,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9372,0.0051,0.0347,0.0010</t>
-  </si>
-  <si>
-    <t>0.5487,0.0004,0.4849,0.0006</t>
-  </si>
-  <si>
-    <t>0.9630,0.0042,0.0045,0.0018</t>
-  </si>
-  <si>
-    <t>0.7619,0.0036,0.1246,0.0130</t>
-  </si>
-  <si>
-    <t>0.0001,0.5671,0.0003,0.9938</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9078,0.0000</t>
-  </si>
-  <si>
-    <t>0.4567,0.6395,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.6500,0.3697,0.0080,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.7888,0.9918,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9799,0.9907,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0078,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0013,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9381,0.0004,0.0432,0.0013</t>
-  </si>
-  <si>
-    <t>0.1592,0.0000,0.9030,0.0001</t>
-  </si>
-  <si>
-    <t>0.4857,0.0030,0.4873,0.0031</t>
-  </si>
-  <si>
-    <t>0.0038,0.0000,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9958,0.2890,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.3110,0.7999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.6145,0.0001,0.0000,0.5888</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0022,0.9994,0.0006</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.2877,0.1057,0.3649,0.0005</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9831,0.0057,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.0774,0.8609,0.0138,0.0036</t>
-  </si>
-  <si>
-    <t>0.9681,0.0034,0.0148,0.0004</t>
-  </si>
-  <si>
-    <t>0.9953,0.0018,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0012,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9538,0.0441,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.4694,0.6729,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.8371,0.2386,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0452,0.0062,0.9693,0.0004</t>
-  </si>
-  <si>
-    <t>0.9869,0.0140,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9974,0.0014,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9757,0.0103,0.0098,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9854,0.0133,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0090,0.0088,0.9542,0.0201</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.1356,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.1445,0.0070,0.8229,0.0018</t>
-  </si>
-  <si>
-    <t>0.0070,0.0007,0.9919,0.0002</t>
-  </si>
-  <si>
-    <t>0.0112,0.0050,0.9726,0.0015</t>
-  </si>
-  <si>
-    <t>0.2076,0.0105,0.7730,0.0007</t>
-  </si>
-  <si>
-    <t>0.0189,0.0247,0.9419,0.0006</t>
-  </si>
-  <si>
-    <t>0.8111,0.0018,0.2577,0.0004</t>
-  </si>
-  <si>
-    <t>0.9100,0.0011,0.0174,0.0205</t>
-  </si>
-  <si>
-    <t>0.5744,0.0015,0.4382,0.0010</t>
-  </si>
-  <si>
-    <t>0.1703,0.8855,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9988,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9389,0.0969,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0758,0.9453,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0266,0.9751,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9810,0.0033,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.8498,0.0003,0.1697,0.0006</t>
-  </si>
-  <si>
-    <t>0.9883,0.0003,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.9720,0.0013,0.0058,0.0023</t>
-  </si>
-  <si>
-    <t>0.2955,0.0004,0.7460,0.0009</t>
-  </si>
-  <si>
-    <t>0.0037,0.0016,0.9953,0.0002</t>
-  </si>
-  <si>
-    <t>0.0044,0.0002,0.9909,0.0013</t>
-  </si>
-  <si>
-    <t>0.0314,0.0123,0.9341,0.0012</t>
-  </si>
-  <si>
-    <t>0.0539,0.0005,0.9572,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.0220,0.9789,0.0013</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9639,0.0277,0.0049,0.0035</t>
-  </si>
-  <si>
-    <t>0.9959,0.0029,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0021,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0146,0.0905,0.8934,0.0019</t>
-  </si>
-  <si>
-    <t>0.9793,0.0003,0.0049,0.0054</t>
-  </si>
-  <si>
-    <t>0.3683,0.0005,0.7926,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0005,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.2667,0.8653,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0160,0.0025,0.9768,0.0009</t>
-  </si>
-  <si>
-    <t>0.0095,0.0014,0.9807,0.0025</t>
-  </si>
-  <si>
-    <t>0.0021,0.0031,0.9918,0.0018</t>
-  </si>
-  <si>
-    <t>0.9669,0.0018,0.0119,0.0011</t>
-  </si>
-  <si>
-    <t>0.9953,0.0001,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9902,0.0112,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9831,0.0212,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0020,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0029,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0067,0.0306,0.9604,0.0012</t>
-  </si>
-  <si>
-    <t>0.0003,0.0021,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0236,0.9893,0.0015</t>
-  </si>
-  <si>
-    <t>0.0018,0.0095,0.9918,0.0004</t>
-  </si>
-  <si>
-    <t>0.0051,0.0000,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0225,0.0000,0.4390,0.1369</t>
-  </si>
-  <si>
-    <t>0.2434,0.0026,0.6595,0.0048</t>
-  </si>
-  <si>
-    <t>0.0046,0.0008,0.9834,0.0216</t>
-  </si>
-  <si>
-    <t>0.9247,0.0000,0.0018,0.0567</t>
-  </si>
-  <si>
-    <t>0.0039,0.0004,0.0000,0.9987</t>
-  </si>
-  <si>
-    <t>0.0177,0.0000,0.0000,0.9984</t>
-  </si>
-  <si>
-    <t>0.9974,0.0001,0.0000,0.0005</t>
+    <t>0.9941,0.0060,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0021,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0201,0.9860,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.0010,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.2378,0.9954,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0012,0.9942,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0776,0.0002,0.5808,0.0373</t>
+  </si>
+  <si>
+    <t>0.0679,0.0005,0.9093,0.0024</t>
+  </si>
+  <si>
+    <t>0.0031,0.0005,0.9903,0.0064</t>
+  </si>
+  <si>
+    <t>0.9038,0.0000,0.0004,0.1405</t>
+  </si>
+  <si>
+    <t>0.0180,0.0035,0.0000,0.9911</t>
+  </si>
+  <si>
+    <t>0.0197,0.0001,0.0000,0.9964</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9981,0.0000,0.0000,0.0004</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1871,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1885,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1899,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1913,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1927,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1941,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1955,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1969,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1983,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1997,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2011,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2025,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2039,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2050,10 +2074,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2067,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2081,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2095,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2109,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2123,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2137,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2151,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2165,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,10 +2200,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2193,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2207,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2221,7 +2245,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2235,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2249,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2260,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2277,7 +2301,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2291,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2305,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2319,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2333,7 +2357,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2347,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2358,10 +2382,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2375,7 +2399,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2389,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2403,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2417,7 +2441,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2431,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2445,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2459,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2470,10 +2494,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2487,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2501,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2515,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2529,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2543,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2557,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2571,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2585,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2599,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2613,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2627,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2641,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2655,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2669,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2683,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2697,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>270</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2711,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2725,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2739,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2753,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2767,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2781,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2795,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2809,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2823,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2837,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2851,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2865,7 +2889,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2876,10 +2900,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2893,7 +2917,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2907,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2921,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2935,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2949,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2963,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2977,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2991,7 +3015,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3005,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3019,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3033,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3044,10 +3068,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,10 +3082,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3075,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3089,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>271</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3103,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3117,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3131,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3145,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3159,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3173,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3187,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3201,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>273</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3215,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3229,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3243,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3257,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3271,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3285,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3299,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3313,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3327,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3338,10 +3362,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3355,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3369,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3383,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3397,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3411,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3425,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3439,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3453,7 +3477,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3467,7 +3491,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3481,7 +3505,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3495,7 +3519,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3506,10 +3530,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3523,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>308</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3537,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>309</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3551,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3565,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3579,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3590,10 +3614,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D126" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3607,7 +3631,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3621,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3635,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3649,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3663,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>375</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3677,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3691,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3705,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3719,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3730,10 +3754,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3747,7 +3771,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3761,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3775,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3789,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3803,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3817,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3831,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3845,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3859,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>266</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3873,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>266</v>
+        <v>396</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3887,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3901,7 +3925,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3915,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3929,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3943,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3957,7 +3981,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3971,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3982,10 +4006,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3999,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>394</v>
+        <v>274</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4013,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4027,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4041,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4052,10 +4076,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4069,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4083,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,10 +4118,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4111,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4125,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4139,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4153,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4167,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4181,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>271</v>
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4195,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4209,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4223,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>407</v>
+        <v>271</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4237,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4251,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4262,10 +4286,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4279,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4290,10 +4314,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4307,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4321,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4335,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4349,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4363,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4377,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4391,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4405,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4419,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4433,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4447,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4461,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4475,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4489,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4503,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4517,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,10 +4552,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4545,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4559,7 +4583,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4573,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4584,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4601,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4615,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4629,7 +4653,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4643,7 +4667,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4657,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4671,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4685,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4699,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4713,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4724,10 +4748,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4741,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4755,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4769,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4783,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4797,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4811,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4825,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4839,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4853,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>373</v>
+        <v>271</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4867,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4881,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4895,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4909,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>271</v>
+        <v>386</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4923,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4937,7 +4961,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4951,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4965,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4979,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4993,7 +5017,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5007,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5021,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5035,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5049,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5063,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5077,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5091,7 +5115,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5105,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5119,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5133,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5147,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>469</v>
+        <v>274</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5161,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5175,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>271</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5189,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5203,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5217,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>473</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5231,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5245,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5259,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5273,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5287,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5298,10 +5322,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5315,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5329,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5343,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5357,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5371,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5385,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>266</v>
+        <v>492</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5399,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>266</v>
+        <v>395</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5413,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
